--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-06-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6FE6B8-8D34-4DEA-8C8A-0947CEE10133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F324628F-2E5F-44FA-A8AD-1612FCB96513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32040" yWindow="645" windowWidth="21600" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33105" yWindow="1125" windowWidth="21600" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -745,9 +745,6 @@
     <t>£791.80</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/140mm-recticel-eurowall-full-fill-cavity-wall-insulation-1200mm-x-460mm</t>
-  </si>
-  <si>
     <t>£562.32</t>
   </si>
   <si>
@@ -827,6 +824,9 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£728.00</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1265,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G3" t="s">
         <v>35</v>
@@ -1377,7 +1377,7 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G4" t="s">
         <v>48</v>
@@ -1433,7 +1433,7 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G5" t="s">
         <v>61</v>
@@ -1489,7 +1489,7 @@
         <v>73</v>
       </c>
       <c r="F6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -1545,7 +1545,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G7" t="s">
         <v>87</v>
@@ -1601,7 +1601,7 @@
         <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G8" t="s">
         <v>87</v>
@@ -1657,7 +1657,7 @@
         <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G9" t="s">
         <v>109</v>
@@ -1713,7 +1713,7 @@
         <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G10" t="s">
         <v>122</v>
@@ -1769,7 +1769,7 @@
         <v>132</v>
       </c>
       <c r="F11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G11" t="s">
         <v>133</v>
@@ -1825,7 +1825,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G12" t="s">
         <v>143</v>
@@ -1881,7 +1881,7 @@
         <v>151</v>
       </c>
       <c r="F13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G13" t="s">
         <v>152</v>
@@ -1937,7 +1937,7 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G14" t="s">
         <v>164</v>
@@ -2049,7 +2049,7 @@
         <v>186</v>
       </c>
       <c r="F16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G16" t="s">
         <v>187</v>
@@ -2073,7 +2073,7 @@
         <v>192</v>
       </c>
       <c r="N16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O16" t="s">
         <v>194</v>
@@ -2096,7 +2096,7 @@
         <v>198</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
@@ -2185,7 +2185,7 @@
         <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O18" t="s">
         <v>204</v>
@@ -2241,7 +2241,7 @@
         <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O19" t="s">
         <v>211</v>
@@ -2253,7 +2253,7 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2456,7 +2456,7 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2465,7 +2465,7 @@
         <v>229</v>
       </c>
       <c r="N23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O23" t="s">
         <v>230</v>
@@ -2512,7 +2512,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2521,7 +2521,7 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O24" t="s">
         <v>236</v>
@@ -2556,19 +2556,19 @@
         <v>26</v>
       </c>
       <c r="G25" t="s">
+        <v>268</v>
+      </c>
+      <c r="H25" t="s">
         <v>241</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
         <v>242</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>243</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -2577,19 +2577,19 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O25" t="s">
+        <v>243</v>
+      </c>
+      <c r="P25" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" t="s">
         <v>244</v>
-      </c>
-      <c r="P25" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>26</v>
-      </c>
-      <c r="R25" t="s">
-        <v>245</v>
       </c>
     </row>
   </sheetData>
